--- a/dataset/problem_one.xlsx
+++ b/dataset/problem_one.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ataraxia\Documents\VscodeDOC\FSSP\FSS\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731B8A06-179A-42FF-95A2-02DDFB7287A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167E0590-EE42-4A15-A0A1-9A332434218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12588" yWindow="4668" windowWidth="23016" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4440" windowWidth="23016" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,13 @@
     <t>MachineSetting</t>
   </si>
   <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>H_60,C_39,F_37,I_21,J_40,A_18,D_61</t>
-  </si>
-  <si>
-    <t>DARES01_A_DA1,DARES02_C_DA1,DARES03_C_DA2,DARES04_D_DA1,DARES05_D_DA1,DARES06_D_DA2,DARES07_D_DA2,DARES08_D_DA3,DARES09_F_DA2,DARES10_F_DA2,DARES11_F_DA3,DARES12_F_DA3,DARES13_F_DA3,DARES14_H_DA1,DARES15_H_DA1,DARES16_H_DA2,DARES17_H_DA3,DARES18_I_DA1,DARES19_I_DA2,DARES20_J_DA1,WBRES01_A_WB1,WBRES02_C_WB1,WBRES03_C_WB1,WBRES04_C_WB1,WBRES05_C_WB1,WBRES06_C_WB1,WBRES07_C_WB1,WBRES08_C_WB1,WBRES09_C_WB2,WBRES10_C_WB2,WBRES11_C_WB2,WBRES12_C_WB2,WBRES13_C_WB2,WBRES14_C_WB2,WBRES15_C_WB2,WBRES16_D_WB1,WBRES17_D_WB1,WBRES18_D_WB2,WBRES19_D_WB3,WBRES20_D_WB3,WBRES21_D_WB3,WBRES22_D_WB3,WBRES23_D_WB3,WBRES24_F_WB2,WBRES25_F_WB2,WBRES26_F_WB2,WBRES27_F_WB3,WBRES28_F_WB3,WBRES29_F_WB3,WBRES30_F_WB3,WBRES31_F_WB3,WBRES32_F_WB3,WBRES33_F_WB3,WBRES34_F_WB3,WBRES35_H_WB3,WBRES36_H_WB3,WBRES37_H_WB3,WBRES38_H_WB3,WBRES39_H_WB3,WBRES40_H_WB3,WBRES41_H_WB3,WBRES42_I_WB2,WBRES43_I_WB2,WBRES44_I_WB2,WBRES45_I_WB2,WBRES46_J_WB1,WBRES47_J_WB1,WBRES48_J_WB2,WBRES49_J_WB2,WBRES50_J_WB2</t>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>J_20,D_30,C_20,F_20,A_10,H_30,I_10</t>
+  </si>
+  <si>
+    <t>DARES01_A_DA1,DARES02_A_DA1,DARES03_A_DA1,DARES04_A_DA1,DARES05_A_DA1,DARES06_A_DA1,DARES07_A_DA1,DARES08_A_DA1,DARES09_C_DA1,DARES10_D_DA3,WBRES01_A_WB1,WBRES02_A_WB1,WBRES03_A_WB1,WBRES04_A_WB1,WBRES05_A_WB1,WBRES06_A_WB1,WBRES07_C_WB1,WBRES08_C_WB1,WBRES09_C_WB1,WBRES10_C_WB1,WBRES11_C_WB1,WBRES12_C_WB2,WBRES13_C_WB2,WBRES14_C_WB2,WBRES15_C_WB2,WBRES16_C_WB2,WBRES17_D_WB1,WBRES18_D_WB2,WBRES19_D_WB2,WBRES20_D_WB2,WBRES21_D_WB2,WBRES22_D_WB2,WBRES23_D_WB2,WBRES24_D_WB3,WBRES25_D_WB3</t>
   </si>
 </sst>
 </file>
